--- a/Catalogo_120_Productos_RepuesTop.xlsx
+++ b/Catalogo_120_Productos_RepuesTop.xlsx
@@ -7186,7 +7186,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:G18"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -7207,6 +7207,9 @@
       <c r="F1" t="str">
         <v>motor</v>
       </c>
+      <c r="G1" t="str">
+        <v>referencia_oem</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -7550,7 +7553,7 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F18"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G18"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -7566,7 +7569,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>VERSION_PLANTILLA: 2.0.0</v>
+        <v>VERSION_PLANTILLA: 2.1.0</v>
       </c>
     </row>
     <row r="3">
